--- a/Data/EXCEL/Transfer/salemon/202208/8054-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8054-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1714CDB5-57F3-4880-A7D9-8C1CA5E31CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6769C195-D5DA-4133-B0FC-861285895DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8054-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,16 +1227,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q252"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="16" width="9.5" customWidth="1"/>
-    <col min="17" max="17" width="11.125" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="5" width="14" customWidth="1"/>
+    <col min="6" max="7" width="15.375" customWidth="1"/>
+    <col min="8" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1255,7 +1263,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1294,7 +1302,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1337,7 +1345,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1376,7 +1384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1429,7 +1437,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1482,7 +1490,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1535,7 +1543,7 @@
         <v>-3.1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1588,7 +1596,7 @@
         <v>-12.4</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1641,7 +1649,7 @@
         <v>-16.399999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1694,7 +1702,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1747,7 +1755,7 @@
         <v>-19.399999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1800,7 +1808,7 @@
         <v>-21.9</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1853,7 +1861,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1906,7 +1914,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1959,7 +1967,7 @@
         <v>35.799999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2012,7 +2020,7 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2065,7 +2073,7 @@
         <v>52.6</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2118,7 +2126,7 @@
         <v>64.3</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2171,7 +2179,7 @@
         <v>85.1</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2224,7 +2232,7 @@
         <v>95.2</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2277,7 +2285,7 @@
         <v>97.6</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2330,7 +2338,7 @@
         <v>86.6</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2383,7 +2391,7 @@
         <v>112.3</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2436,7 +2444,7 @@
         <v>75.099999999999994</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2489,7 +2497,7 @@
         <v>-2.98</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2542,7 +2550,7 @@
         <v>-5.47</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2595,7 +2603,7 @@
         <v>-8.11</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2648,7 +2656,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2701,7 +2709,7 @@
         <v>-17.5</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2754,7 +2762,7 @@
         <v>-20.100000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2807,7 +2815,7 @@
         <v>-25.3</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2860,7 +2868,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2913,7 +2921,7 @@
         <v>-31.1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2966,7 +2974,7 @@
         <v>-29</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3019,7 +3027,7 @@
         <v>-36.1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3072,7 +3080,7 @@
         <v>-23.9</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3125,7 +3133,7 @@
         <v>-32</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3178,7 +3186,7 @@
         <v>-32.1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3231,7 +3239,7 @@
         <v>-33</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3284,7 +3292,7 @@
         <v>-33.4</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3337,7 +3345,7 @@
         <v>-33.9</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3390,7 +3398,7 @@
         <v>-34.6</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3443,7 +3451,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3496,7 +3504,7 @@
         <v>-30.7</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3549,7 +3557,7 @@
         <v>-24.2</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3602,7 +3610,7 @@
         <v>-15.9</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3655,7 +3663,7 @@
         <v>-9.56</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3708,7 +3716,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3761,7 +3769,7 @@
         <v>-10.5</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3814,7 +3822,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3867,7 +3875,7 @@
         <v>-11.4</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3920,7 +3928,7 @@
         <v>-10.5</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3973,7 +3981,7 @@
         <v>-9.15</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4026,7 +4034,7 @@
         <v>-10.199999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4079,7 +4087,7 @@
         <v>-8.43</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4132,7 +4140,7 @@
         <v>-7.7</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4185,7 +4193,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4238,7 +4246,7 @@
         <v>-12.6</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4291,7 +4299,7 @@
         <v>-11.5</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4344,7 +4352,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4397,7 +4405,7 @@
         <v>-7.59</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4450,7 +4458,7 @@
         <v>-6.97</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4503,7 +4511,7 @@
         <v>-6.08</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4556,7 +4564,7 @@
         <v>-6.05</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4609,7 +4617,7 @@
         <v>-7.15</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4662,7 +4670,7 @@
         <v>-6.66</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4715,7 +4723,7 @@
         <v>-8.64</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4768,7 +4776,7 @@
         <v>-11.1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4821,7 +4829,7 @@
         <v>-12.5</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4874,7 +4882,7 @@
         <v>-12.9</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4927,7 +4935,7 @@
         <v>-12.1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4980,7 +4988,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5033,7 +5041,7 @@
         <v>-8.6199999999999992</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5086,7 +5094,7 @@
         <v>-6.52</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5139,7 +5147,7 @@
         <v>-6.3</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5192,7 +5200,7 @@
         <v>-5.54</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5245,7 +5253,7 @@
         <v>-5.24</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5298,7 +5306,7 @@
         <v>-5.5</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5351,7 +5359,7 @@
         <v>-7.65</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5404,7 +5412,7 @@
         <v>-7.46</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5457,7 +5465,7 @@
         <v>-9.7799999999999994</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5510,7 +5518,7 @@
         <v>-14.2</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5563,7 +5571,7 @@
         <v>-24.6</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5616,7 +5624,7 @@
         <v>-20.399999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5669,7 +5677,7 @@
         <v>-15.4</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5722,7 +5730,7 @@
         <v>-16.3</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5775,7 +5783,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5828,7 +5836,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5881,7 +5889,7 @@
         <v>-15.5</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5934,7 +5942,7 @@
         <v>-14.6</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5987,7 +5995,7 @@
         <v>-12.7</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6040,7 +6048,7 @@
         <v>-12.1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6093,7 +6101,7 @@
         <v>-12.5</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6146,7 +6154,7 @@
         <v>-14.2</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6199,7 +6207,7 @@
         <v>-11.3</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6252,7 +6260,7 @@
         <v>-0.39</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6305,7 +6313,7 @@
         <v>-2.44</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6358,7 +6366,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6411,7 +6419,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6464,7 +6472,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6517,7 +6525,7 @@
         <v>8.52</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6570,7 +6578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6623,7 +6631,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6676,7 +6684,7 @@
         <v>9.2799999999999994</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6729,7 +6737,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6782,7 +6790,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6835,7 +6843,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6888,7 +6896,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6941,7 +6949,7 @@
         <v>-0.52</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -6994,7 +7002,7 @@
         <v>-4.8099999999999996</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7047,7 +7055,7 @@
         <v>-9.1199999999999992</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7100,7 +7108,7 @@
         <v>-11.9</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7153,7 +7161,7 @@
         <v>-15.4</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7206,7 +7214,7 @@
         <v>-18.899999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7259,7 +7267,7 @@
         <v>-17.7</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7312,7 +7320,7 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7365,7 +7373,7 @@
         <v>-22.9</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7418,7 +7426,7 @@
         <v>-27.7</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7471,7 +7479,7 @@
         <v>-30.6</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7524,7 +7532,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7577,7 +7585,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7630,7 +7638,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7683,7 +7691,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7736,7 +7744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41122</v>
       </c>
@@ -7789,7 +7797,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41091</v>
       </c>
@@ -7842,7 +7850,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41061</v>
       </c>
@@ -7895,7 +7903,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41030</v>
       </c>
@@ -7948,7 +7956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>41000</v>
       </c>
@@ -8001,7 +8009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40969</v>
       </c>
@@ -8054,7 +8062,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40940</v>
       </c>
@@ -8107,7 +8115,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>40909</v>
       </c>
@@ -8160,7 +8168,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>40878</v>
       </c>
@@ -8213,7 +8221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>40848</v>
       </c>
@@ -8266,7 +8274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>40817</v>
       </c>
@@ -8319,7 +8327,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>40787</v>
       </c>
@@ -8372,7 +8380,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>40756</v>
       </c>
@@ -8425,7 +8433,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>40725</v>
       </c>
@@ -8478,7 +8486,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="5" customFormat="1">
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>40695</v>
       </c>
@@ -8531,7 +8539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:17" s="5" customFormat="1">
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>40664</v>
       </c>
@@ -8584,7 +8592,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="5" customFormat="1">
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>40634</v>
       </c>
@@ -8637,7 +8645,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="5" customFormat="1">
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>40603</v>
       </c>
@@ -8690,7 +8698,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="5" customFormat="1">
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>40575</v>
       </c>
@@ -8743,7 +8751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" s="5" customFormat="1">
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>40544</v>
       </c>
@@ -8796,7 +8804,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="5" customFormat="1">
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>40513</v>
       </c>
@@ -8849,7 +8857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="5" customFormat="1">
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>40483</v>
       </c>
@@ -8902,7 +8910,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="5" customFormat="1">
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>40452</v>
       </c>
@@ -8955,7 +8963,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="5" customFormat="1">
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>40422</v>
       </c>
@@ -9008,7 +9016,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:17" s="5" customFormat="1">
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>40391</v>
       </c>
@@ -9061,7 +9069,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:17" s="5" customFormat="1">
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>40360</v>
       </c>
@@ -9114,7 +9122,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:17" s="5" customFormat="1">
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>40330</v>
       </c>
@@ -9167,7 +9175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:17" s="5" customFormat="1">
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>40299</v>
       </c>
@@ -9220,7 +9228,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:17" s="5" customFormat="1">
+    <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>40269</v>
       </c>
@@ -9273,7 +9281,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:17" s="5" customFormat="1">
+    <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>40238</v>
       </c>
@@ -9326,7 +9334,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:17" s="5" customFormat="1">
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>40210</v>
       </c>
@@ -9379,7 +9387,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:17" s="5" customFormat="1">
+    <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>40179</v>
       </c>
@@ -9432,7 +9440,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:17" s="5" customFormat="1">
+    <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>40148</v>
       </c>
@@ -9485,7 +9493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:17" s="5" customFormat="1">
+    <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>40118</v>
       </c>
@@ -9538,7 +9546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" s="5" customFormat="1">
+    <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>40087</v>
       </c>
@@ -9591,7 +9599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:17" s="5" customFormat="1">
+    <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>40057</v>
       </c>
@@ -9644,7 +9652,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:17" s="5" customFormat="1">
+    <row r="161" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>40026</v>
       </c>
@@ -9697,7 +9705,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:17" s="5" customFormat="1">
+    <row r="162" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>39995</v>
       </c>
@@ -9750,7 +9758,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:17" s="5" customFormat="1">
+    <row r="163" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>39965</v>
       </c>
@@ -9803,7 +9811,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:17" s="5" customFormat="1">
+    <row r="164" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>39934</v>
       </c>
@@ -9856,7 +9864,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:17" s="5" customFormat="1">
+    <row r="165" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>39904</v>
       </c>
@@ -9909,7 +9917,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:17" s="5" customFormat="1">
+    <row r="166" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>39873</v>
       </c>
@@ -9962,7 +9970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:17" s="5" customFormat="1">
+    <row r="167" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>39845</v>
       </c>
@@ -10015,7 +10023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:17" s="5" customFormat="1">
+    <row r="168" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>39814</v>
       </c>
@@ -10068,7 +10076,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:17" s="5" customFormat="1">
+    <row r="169" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>39783</v>
       </c>
@@ -10121,7 +10129,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:17" s="5" customFormat="1">
+    <row r="170" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>39753</v>
       </c>
@@ -10174,7 +10182,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:17" s="5" customFormat="1">
+    <row r="171" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>39722</v>
       </c>
@@ -10227,7 +10235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:17" s="5" customFormat="1">
+    <row r="172" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>39692</v>
       </c>
@@ -10280,7 +10288,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:17" s="5" customFormat="1">
+    <row r="173" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>39661</v>
       </c>
@@ -10333,7 +10341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:17" s="5" customFormat="1">
+    <row r="174" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>39630</v>
       </c>
@@ -10386,7 +10394,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:17" s="5" customFormat="1">
+    <row r="175" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>39600</v>
       </c>
@@ -10439,7 +10447,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:17" s="5" customFormat="1">
+    <row r="176" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>39569</v>
       </c>
@@ -10492,7 +10500,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:17" s="5" customFormat="1">
+    <row r="177" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>39539</v>
       </c>
@@ -10545,7 +10553,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:17" s="5" customFormat="1">
+    <row r="178" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>39508</v>
       </c>
@@ -10598,7 +10606,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:17" s="5" customFormat="1">
+    <row r="179" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>39479</v>
       </c>
@@ -10651,7 +10659,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:17" s="5" customFormat="1">
+    <row r="180" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>39448</v>
       </c>
@@ -10704,7 +10712,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:17" s="5" customFormat="1">
+    <row r="181" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>39417</v>
       </c>
@@ -10757,7 +10765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:17" s="5" customFormat="1">
+    <row r="182" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>39387</v>
       </c>
@@ -10810,7 +10818,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:17" s="5" customFormat="1">
+    <row r="183" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>39356</v>
       </c>
@@ -10863,7 +10871,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:17" s="5" customFormat="1">
+    <row r="184" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>39326</v>
       </c>
@@ -10916,7 +10924,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:17" s="5" customFormat="1">
+    <row r="185" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>39295</v>
       </c>
@@ -10969,7 +10977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:17" s="5" customFormat="1">
+    <row r="186" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>39264</v>
       </c>
@@ -11022,7 +11030,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:17" s="5" customFormat="1">
+    <row r="187" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>39234</v>
       </c>
@@ -11075,7 +11083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:17" s="5" customFormat="1">
+    <row r="188" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>39203</v>
       </c>
@@ -11128,7 +11136,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:17" s="5" customFormat="1">
+    <row r="189" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>39173</v>
       </c>
@@ -11181,7 +11189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:17" s="5" customFormat="1">
+    <row r="190" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>39142</v>
       </c>
@@ -11234,7 +11242,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="191" spans="1:17" s="5" customFormat="1">
+    <row r="191" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>39114</v>
       </c>
@@ -11287,7 +11295,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:17" s="5" customFormat="1">
+    <row r="192" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>39083</v>
       </c>
@@ -11340,7 +11348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:17" s="5" customFormat="1">
+    <row r="193" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>39052</v>
       </c>
@@ -11393,7 +11401,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:17" s="5" customFormat="1">
+    <row r="194" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>39022</v>
       </c>
@@ -11446,7 +11454,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:17" s="5" customFormat="1">
+    <row r="195" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>38991</v>
       </c>
@@ -11499,7 +11507,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:17" s="5" customFormat="1">
+    <row r="196" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>38961</v>
       </c>
@@ -11552,7 +11560,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:17" s="5" customFormat="1">
+    <row r="197" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>38930</v>
       </c>
@@ -11605,7 +11613,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:17" s="5" customFormat="1">
+    <row r="198" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>38899</v>
       </c>
@@ -11658,7 +11666,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:17" s="5" customFormat="1">
+    <row r="199" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>38869</v>
       </c>
@@ -11711,7 +11719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:17" s="5" customFormat="1">
+    <row r="200" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>38838</v>
       </c>
@@ -11764,7 +11772,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:17" s="5" customFormat="1">
+    <row r="201" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>38808</v>
       </c>
@@ -11817,7 +11825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:17" s="5" customFormat="1">
+    <row r="202" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>38777</v>
       </c>
@@ -11870,7 +11878,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:17" s="5" customFormat="1">
+    <row r="203" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>38749</v>
       </c>
@@ -11923,7 +11931,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:17" s="5" customFormat="1">
+    <row r="204" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>38718</v>
       </c>
@@ -11976,7 +11984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:17" s="5" customFormat="1">
+    <row r="205" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>38687</v>
       </c>
@@ -12029,7 +12037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:17" s="5" customFormat="1">
+    <row r="206" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>38657</v>
       </c>
@@ -12082,7 +12090,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:17" s="5" customFormat="1">
+    <row r="207" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>38626</v>
       </c>
@@ -12135,7 +12143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:17" s="5" customFormat="1">
+    <row r="208" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>38596</v>
       </c>
@@ -12188,7 +12196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:17" s="5" customFormat="1">
+    <row r="209" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>38565</v>
       </c>
@@ -12241,7 +12249,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:17" s="5" customFormat="1">
+    <row r="210" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>38534</v>
       </c>
@@ -12294,7 +12302,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:17" s="5" customFormat="1">
+    <row r="211" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>38504</v>
       </c>
@@ -12347,7 +12355,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:17" s="5" customFormat="1">
+    <row r="212" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>38473</v>
       </c>
@@ -12400,7 +12408,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:17" s="5" customFormat="1">
+    <row r="213" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>38443</v>
       </c>
@@ -12453,7 +12461,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:17" s="5" customFormat="1">
+    <row r="214" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>38412</v>
       </c>
@@ -12506,7 +12514,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:17" s="5" customFormat="1">
+    <row r="215" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>38384</v>
       </c>
@@ -12559,7 +12567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:17" s="5" customFormat="1">
+    <row r="216" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>38353</v>
       </c>
@@ -12612,7 +12620,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:17" s="5" customFormat="1">
+    <row r="217" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>38322</v>
       </c>
@@ -12665,7 +12673,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:17" s="5" customFormat="1">
+    <row r="218" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>38292</v>
       </c>
@@ -12718,7 +12726,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:17" s="5" customFormat="1">
+    <row r="219" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>38261</v>
       </c>
@@ -12771,7 +12779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:17" s="5" customFormat="1">
+    <row r="220" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>38231</v>
       </c>
@@ -12824,7 +12832,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:17" s="5" customFormat="1">
+    <row r="221" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>38200</v>
       </c>
@@ -12877,7 +12885,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:17" s="5" customFormat="1">
+    <row r="222" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>38169</v>
       </c>
@@ -12930,7 +12938,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:17" s="5" customFormat="1">
+    <row r="223" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>38139</v>
       </c>
@@ -12983,7 +12991,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:17" s="5" customFormat="1">
+    <row r="224" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>38108</v>
       </c>
@@ -13036,7 +13044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:17" s="5" customFormat="1">
+    <row r="225" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>38078</v>
       </c>
@@ -13089,7 +13097,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:17" s="5" customFormat="1">
+    <row r="226" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>38047</v>
       </c>
@@ -13142,7 +13150,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:17" s="5" customFormat="1">
+    <row r="227" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>38018</v>
       </c>
@@ -13195,7 +13203,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:17" s="5" customFormat="1">
+    <row r="228" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>37987</v>
       </c>
@@ -13248,7 +13256,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:17" s="5" customFormat="1">
+    <row r="229" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>37956</v>
       </c>
@@ -13301,7 +13309,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:17" s="5" customFormat="1">
+    <row r="230" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>37926</v>
       </c>
@@ -13354,7 +13362,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:17" s="5" customFormat="1">
+    <row r="231" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>37895</v>
       </c>
@@ -13407,7 +13415,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:17" s="5" customFormat="1">
+    <row r="232" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>37865</v>
       </c>
@@ -13460,7 +13468,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:17" s="5" customFormat="1">
+    <row r="233" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>37834</v>
       </c>
@@ -13513,7 +13521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:17" s="5" customFormat="1">
+    <row r="234" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>37803</v>
       </c>
@@ -13566,7 +13574,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:17" s="5" customFormat="1">
+    <row r="235" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>37773</v>
       </c>
@@ -13619,7 +13627,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:17" s="5" customFormat="1">
+    <row r="236" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>37742</v>
       </c>
@@ -13672,7 +13680,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:17" s="5" customFormat="1">
+    <row r="237" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>37712</v>
       </c>
@@ -13725,7 +13733,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:17" s="5" customFormat="1">
+    <row r="238" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>37681</v>
       </c>
@@ -13778,7 +13786,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:17" s="5" customFormat="1">
+    <row r="239" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>37653</v>
       </c>
@@ -13831,7 +13839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:17" s="5" customFormat="1">
+    <row r="240" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>37622</v>
       </c>
@@ -13884,7 +13892,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="241" spans="1:17" s="5" customFormat="1">
+    <row r="241" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A241" s="6">
         <v>37591</v>
       </c>
@@ -13937,7 +13945,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:17" s="5" customFormat="1">
+    <row r="242" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A242" s="6">
         <v>37561</v>
       </c>
@@ -13990,7 +13998,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:17" s="5" customFormat="1">
+    <row r="243" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A243" s="6">
         <v>37530</v>
       </c>
@@ -14043,7 +14051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="244" spans="1:17" s="5" customFormat="1">
+    <row r="244" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A244" s="6">
         <v>37500</v>
       </c>
@@ -14096,7 +14104,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:17" s="5" customFormat="1">
+    <row r="245" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A245" s="6">
         <v>37469</v>
       </c>
@@ -14149,7 +14157,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="246" spans="1:17" s="5" customFormat="1">
+    <row r="246" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A246" s="6">
         <v>37438</v>
       </c>
@@ -14202,7 +14210,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="247" spans="1:17" s="5" customFormat="1">
+    <row r="247" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A247" s="6">
         <v>37408</v>
       </c>
@@ -14255,7 +14263,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="248" spans="1:17" s="5" customFormat="1">
+    <row r="248" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A248" s="6">
         <v>37377</v>
       </c>
@@ -14308,7 +14316,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="249" spans="1:17" s="5" customFormat="1">
+    <row r="249" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A249" s="6">
         <v>37347</v>
       </c>
@@ -14361,7 +14369,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:17" s="5" customFormat="1">
+    <row r="250" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A250" s="6">
         <v>37316</v>
       </c>
@@ -14414,7 +14422,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="251" spans="1:17" s="5" customFormat="1">
+    <row r="251" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A251" s="6">
         <v>37288</v>
       </c>
@@ -14467,7 +14475,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="252" spans="1:17" s="5" customFormat="1">
+    <row r="252" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A252" s="6">
         <v>37257</v>
       </c>
@@ -14535,7 +14543,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>